--- a/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:31</t>
+          <t>2026-09-02 00:57:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:32</t>
+          <t>2026-09-02 00:57:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:34</t>
+          <t>2026-09-02 00:57:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:00</t>
+          <t>2026-09-02 01:22:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:01</t>
+          <t>2026-09-02 01:22:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:57:02</t>
+          <t>2026-09-02 01:22:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>-2.25%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>-0.93%4275</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4315</v>
+        <v>4275</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.21%14150</t>
+          <t>-2.01%13865</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14150</v>
+        <v>13865</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>0%2610</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7800</v>
+        <v>2610</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>-1.95%5770</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5885</v>
+        <v>5770</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>-2.22%5290</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5410</v>
+        <v>5290</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.92%7580</t>
+          <t>+3.03%7810</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7580</v>
+        <v>7810</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>-2.93%3310</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3410</v>
+        <v>3310</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.72%5995</t>
+          <t>-1.67%5895</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5995</v>
+        <v>5895</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.57%2030</t>
+          <t>-2.71%1975</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2030</v>
+        <v>1975</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+8.99%994</t>
+          <t>-2.72%967</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+8.99%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>994</v>
+        <v>967</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>+3.53%17725</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>17120</v>
+        <v>17725</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>+0.21%973</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1865</v>
+        <v>1730</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:46</t>
+          <t>2026-09-02 16:26:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.23%1375</t>
+          <t>-2.55%1340</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1375</v>
+        <v>1340</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>-3.46%5445</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5640</v>
+        <v>5445</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1450</v>
+        <v>1410</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2315</v>
+        <v>2170</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.31%503</t>
+          <t>-0.2%502</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>-2.95%2140</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+8.35%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2205</v>
+        <v>2140</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.69%145</t>
+          <t>-1.03%143.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>145</v>
+        <v>143.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.3%234.5</t>
+          <t>+1.28%237.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>234.5</v>
+        <v>237.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+5.15%1225</t>
+          <t>-4.08%1175</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+5.15%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1225</v>
+        <v>1175</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.99%66.7</t>
+          <t>0%66.7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+10%2640</t>
+          <t>-9.28%2395</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-9.28%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2640</v>
+        <v>2395</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%196</t>
+          <t>-4.59%187</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.48%731</t>
+          <t>-6.16%686</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-6.16%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>731</v>
+        <v>686</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+3.3%2345</t>
+          <t>-1.92%2300</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2345</v>
+        <v>2300</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:47</t>
+          <t>2026-09-02 16:26:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.97%3425</t>
+          <t>-0.88%3395</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3425</v>
+        <v>3395</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.41%252</t>
+          <t>-1.19%249</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+8.56%279</t>
+          <t>-3.05%270.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+8.56%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>279</v>
+        <v>270.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+2.71%132.5</t>
+          <t>-4.91%126</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>132.5</v>
+        <v>126</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.31%1635</t>
+          <t>+9.79%1795</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+9.79%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1635</v>
+        <v>1795</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+2.4%256</t>
+          <t>-1.95%251</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.03%342</t>
+          <t>-1.46%337</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.03%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.32%153.5</t>
+          <t>-2.61%149.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>153.5</v>
+        <v>149.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.48%600</t>
+          <t>+4%624</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+4%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+9.94%6910</t>
+          <t>+2.03%7050</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6910</v>
+        <v>7050</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.24%421.5</t>
+          <t>-0.47%419.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>421.5</v>
+        <v>419.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.17%5870</t>
+          <t>-2.73%5710</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5870</v>
+        <v>5710</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+4.85%540</t>
+          <t>-0.93%535</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+4.85%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.14%173</t>
+          <t>-2.6%168.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>173</v>
+        <v>168.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.6%711</t>
+          <t>-0.42%708</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:48</t>
+          <t>2026-09-02 16:26:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.76%800</t>
+          <t>-3.25%774</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>800</v>
+        <v>774</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">

--- a/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.58%1,034,000</t>
+          <t>8.55%1,034,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.58%</t>
+          <t>8.55%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.90%470,000</t>
+          <t>6.97%470,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.90%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>0%2610</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>13865</v>
+        <v>2610</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.92%123,000</t>
+          <t>5.97%659,197</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>5.97%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>123000</v>
+        <v>659197</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-2.01%13865</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2610</v>
+        <v>13865</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.86%221,000</t>
+          <t>5.91%123,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>5.91%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>221000</v>
+        <v>123000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.38%238,000</t>
+          <t>4.37%238,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>4.37%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.97%154,000</t>
+          <t>4.17%154,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-1.67%5895</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3310</v>
+        <v>5895</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.90%336,000</t>
+          <t>3.88%190,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>336000</v>
+        <v>190000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.67%5895</t>
+          <t>-2.93%3310</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5895</v>
+        <v>3310</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.87%190,000</t>
+          <t>3.86%336,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>190000</v>
+        <v>336000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>5274信 驊</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>+3.53%17725</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1975</v>
+        <v>17725</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.25%470,000</t>
+          <t>3.22%52,400</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>470000</v>
+        <v>52400</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,34 +1114,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.72%967</t>
+          <t>-2.71%1975</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.72%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>967</v>
+        <v>1975</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.17%938,000</t>
+          <t>3.22%470,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>938000</v>
+        <v>470000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5274信 驊</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>-2.72%967</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>17725</v>
+        <v>967</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.05%52,400</t>
+          <t>3.15%938,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>52400</v>
+        <v>938000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.00%907,000</t>
+          <t>3.06%907,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6187萬 潤</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>-2.55%1340</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1730</v>
+        <v>1340</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.83%446,000</t>
+          <t>2.77%596,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>446000</v>
+        <v>596000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:46</t>
+          <t>2026-09-02 19:50:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6187萬 潤</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.55%1340</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1340</v>
+        <v>1730</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.79%596,000</t>
+          <t>2.68%446,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>596000</v>
+        <v>446000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.36%123,000</t>
+          <t>2.32%123,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.95%395,000</t>
+          <t>1.93%395,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,25 +1541,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-0.2%502</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2170</v>
+        <v>502</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.80%228,000</t>
+          <t>1.80%1,034,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>228000</v>
+        <v>1034000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.2%502</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>502</v>
+        <v>2170</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.77%1,034,000</t>
+          <t>1.72%228,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1034000</v>
+        <v>228000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.70%227,000</t>
+          <t>1.68%227,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.53%3,104,000</t>
+          <t>1.54%3,104,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.48%1,861,000</t>
+          <t>1.53%1,861,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-4.08%1175</t>
+          <t>0%66.7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1175</v>
+        <v>66.7</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.47%353,000</t>
+          <t>1.45%6,267,040</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>353000</v>
+        <v>6267040</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0%66.7</t>
+          <t>-4.08%1175</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>66.7</v>
+        <v>1175</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.42%6,267,040</t>
+          <t>1.44%353,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>6267040</v>
+        <v>353000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>6442光 聖</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.28%2395</t>
+          <t>+9.79%1795</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.28%</t>
+          <t>+9.79%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2395</v>
+        <v>1795</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.10%122,000</t>
+          <t>1.01%163,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>122000</v>
+        <v>163000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.59%187</t>
+          <t>-9.28%2395</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>-9.28%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>187</v>
+        <v>2395</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.02%1,532,000</t>
+          <t>1.01%122,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1532000</v>
+        <v>122000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.16%686</t>
+          <t>-4.59%187</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.16%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>686</v>
+        <v>187</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.00%404,000</t>
+          <t>0.99%1,532,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>404000</v>
+        <v>1532000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3081聯 亞</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>-0.88%3395</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>589</v>
+        <v>3395</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.96%464,000</t>
+          <t>0.97%82,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>464000</v>
+        <v>82000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:48</t>
+          <t>2026-09-02 19:50:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3081聯 亞</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.88%3395</t>
+          <t>-6.16%686</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-6.16%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3395</v>
+        <v>686</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.96%82,000</t>
+          <t>0.96%404,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>82000</v>
+        <v>404000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.95%1,107,336</t>
+          <t>0.96%1,107,336</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.05%270.5</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>270.5</v>
+        <v>589</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.95%999,000</t>
+          <t>0.95%464,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>999000</v>
+        <v>464000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-3.05%270.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>126</v>
+        <v>270.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.94%2,096,000</t>
+          <t>0.94%999,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2096000</v>
+        <v>999000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6442光 聖</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+9.79%1795</t>
+          <t>-4.91%126</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+9.79%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1795</v>
+        <v>126</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.91%163,000</t>
+          <t>0.92%2,096,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>163000</v>
+        <v>2096000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.77%664,000</t>
+          <t>0.78%664,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.71%1,351,000</t>
+          <t>0.70%1,351,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.60%293,000</t>
+          <t>0.63%293,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.49%21,000</t>
+          <t>0.51%21,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3145,12 +3145,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.32%133,000</t>
+          <t>0.33%133,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:49</t>
+          <t>2026-09-02 19:50:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:02</t>
+          <t>2026-09-02 22:22:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:03</t>
+          <t>2026-09-02 22:22:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 19:50:04</t>
+          <t>2026-09-02 22:22:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
